--- a/docs/requirements-v1.04.xlsx
+++ b/docs/requirements-v1.04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E99B79-5F05-4F96-A378-7C8DF5D9A248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E616822-15D3-4D7B-9093-8C689CBFDC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="3630" windowWidth="14610" windowHeight="7845" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="3630" windowWidth="14610" windowHeight="7845" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -940,31 +940,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・一番上に、全体の進み具合のゲージを細く1本出す(F6)。その下に今日のリンク(F21)を出す
-・その下は役割ごとに3段に分ける。1段目:1行入力の欄(F17)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」。記録中の作業(F4)は、トップではなく画面の切り替えのすぐ下に小さく出す(UI 試作で変更)
-・2段目に出すものは次の9つ:①(なし。作業記録を全自動にしたので、再開の確認はなくした。基本設計 Q25)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F7・F9・F10・F11・F12・F19。Claude の締切の読み取り F9・F11・F20 も含む)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
-・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に、今日の時間と明日の時間(F10・F12)を出す(明日の時間は基本設計で本人の希望により追加)。今日の時間には、授業・面接など時刻の決まった予定だけを出し、タスクの締切は出さない(今日が締切のタスクは「今日」の欄にだけ出す)
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
-・「未分類」のタスクのラベルは灰色にする(F1)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
-済:締切が同じときの並び順 → 時刻順 → 「先に並べる」設定の種類が先(初めは大学・就活)→ 登録が古い順
-済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は種類ごとの色(F1。未分類は灰色)
-済(点検で追加):2段目に何を出すか → 9つに決めた
-・1行入力の欄(F17)と、着手日で「今日」に上がったタスク(F16)の、トップでの置き場所と並び順
-・「今週」の範囲(何曜日から何曜日までか。F17 の「金」の読み方もこれに合わせる)
-→ 基本設計で決める
-済(基本設計):上の「基本設計で決める」は、基本設計書の疑問点 Q3・Q4 で決めた
-済(UI 試作で変更):記録中の作業は1段目からはずし、画面の切り替えのすぐ下に小さく1行で出す。1段目は1行入力の欄にした</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>・作業記録は全自動でつける。1分ごとに、PC で前に出ているアプリの画面の名前(画面の中身は見ない)から入れ物を判断して記録する(基本設計 Q23・Q25)
 ・同じ入れ物が続く間を1つの記録にする。どの入れ物か判断できない時間は記録しない
 ・初めて見た画面の名前は、連絡の画面で「どの入れ物の作業ですか?」と聞き、答えを覚える。作業でないものは「記録しない」と答え、それも覚える
@@ -1116,6 +1091,31 @@
   </si>
   <si>
     <t>Windows 11 の PC。次がそろっていること:Chrome/Outlook アプリ(クラシック版、大学のアカウントでサインイン済み)/Claude Code(ログイン済み。F9・F10・F11・F14・F17・F18・F20・F22 で使う)/Google アカウントの許可(F11〜F13 で使う)/モーニングブリーフの時間割ファイル timetable.md(F10 で使う)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・一番上に、全体の進み具合のゲージを細く1本出す(F6)。その下に今日のリンク(F21)を出す
+・その下は役割ごとに段に分ける。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」。もとの1段目(記録中の作業 F4)は、トップではなく画面の切り替えのすぐ下に小さく出す(UI 試作で変更。「2段目」「3段目」の呼び方は、ほかの機能から指しているのでそのまま使う)。「期限切れ」の下に1行入力の欄(F17)を置く
+・2段目に出すものは次の9つ:①(なし。作業記録を全自動にしたので、再開の確認はなくした。基本設計 Q25)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F7・F9・F10・F11・F12・F19。Claude の締切の読み取り F9・F11・F20 も含む)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間と明日の時間(F10・F12)を出す(明日の時間は基本設計で本人の希望により追加)。今日の時間には、授業・面接など時刻の決まった予定だけを出し、タスクの締切は出さない(今日が締切のタスクは「今日」の欄にだけ出す)
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
+・「未分類」のタスクのラベルは灰色にする(F1)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
+済:締切が同じときの並び順 → 時刻順 → 「先に並べる」設定の種類が先(初めは大学・就活)→ 登録が古い順
+済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は種類ごとの色(F1。未分類は灰色)
+済(点検で追加):2段目に何を出すか → 9つに決めた
+・1行入力の欄(F17)と、着手日で「今日」に上がったタスク(F16)の、トップでの置き場所と並び順
+・「今週」の範囲(何曜日から何曜日までか。F17 の「金」の読み方もこれに合わせる)
+→ 基本設計で決める
+済(基本設計):上の「基本設計で決める」は、基本設計書の疑問点 Q3・Q4 で決めた
+済(UI 試作で変更):記録中の作業は1段目からはずし、画面の切り替えのすぐ下に小さく1行で出す。F18 ③の「○○で終わったタスクはある?」は2段目のお知らせに出す</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1317,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1387,9 +1387,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1859,7 +1856,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="115.5">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2008,14 +2005,14 @@
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="31" t="s">
         <v>214</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="33">
+      <c r="E12" s="32">
         <v>46313</v>
       </c>
       <c r="F12" s="4"/>
@@ -2205,7 +2202,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="49.5">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2213,7 +2210,7 @@
       <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
         <v>215</v>
       </c>
       <c r="C5" s="8"/>
@@ -2288,7 +2285,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="49.5">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2325,13 +2322,13 @@
       <c r="C6" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="31" t="s">
         <v>216</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="31" t="s">
         <v>217</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -2346,13 +2343,13 @@
       <c r="C7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="31" t="s">
         <v>218</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="31" t="s">
         <v>219</v>
       </c>
       <c r="G7" s="10" t="s">
@@ -2367,14 +2364,14 @@
       <c r="C8" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D8" s="32" t="s">
-        <v>220</v>
+      <c r="D8" s="10" t="s">
+        <v>237</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>221</v>
+      <c r="F8" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>87</v>
@@ -2388,8 +2385,8 @@
       <c r="C9" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="32" t="s">
-        <v>222</v>
+      <c r="D9" s="31" t="s">
+        <v>220</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>39</v>
@@ -2430,14 +2427,14 @@
       <c r="C11" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D11" s="32" t="s">
-        <v>223</v>
+      <c r="D11" s="31" t="s">
+        <v>221</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="32" t="s">
-        <v>224</v>
+      <c r="F11" s="31" t="s">
+        <v>222</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>90</v>
@@ -2493,14 +2490,14 @@
       <c r="C14" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D14" s="32" t="s">
-        <v>225</v>
+      <c r="D14" s="31" t="s">
+        <v>223</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="32" t="s">
-        <v>226</v>
+      <c r="F14" s="31" t="s">
+        <v>224</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>93</v>
@@ -2598,14 +2595,14 @@
       <c r="C19" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="32" t="s">
-        <v>227</v>
+      <c r="D19" s="31" t="s">
+        <v>225</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="32" t="s">
-        <v>228</v>
+      <c r="F19" s="31" t="s">
+        <v>226</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>129</v>
@@ -2703,14 +2700,14 @@
       <c r="C24" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="34" t="s">
-        <v>229</v>
+      <c r="D24" s="33" t="s">
+        <v>227</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="34" t="s">
-        <v>230</v>
+      <c r="F24" s="33" t="s">
+        <v>228</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>152</v>
@@ -2758,23 +2755,23 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="324">
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="D27" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="E27" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="G27" s="33" t="s">
         <v>233</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2803,7 +2800,7 @@
       </c>
     </row>
     <row r="3" spans="1:1" ht="82.5">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2897,8 +2894,8 @@
       <c r="B8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>236</v>
+      <c r="C8" s="31" t="s">
+        <v>234</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>56</v>
@@ -3051,8 +3048,8 @@
       <c r="B19" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>237</v>
+      <c r="C19" s="33" t="s">
+        <v>235</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>65</v>
@@ -3093,8 +3090,8 @@
       <c r="B22" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>238</v>
+      <c r="C22" s="33" t="s">
+        <v>236</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>65</v>
